--- a/Excel/ExchangeConfig.xlsx
+++ b/Excel/ExchangeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -59,13 +59,13 @@
     <t>150</t>
   </si>
   <si>
-    <t>怒斩自选</t>
-  </si>
-  <si>
-    <t>噬魂自选</t>
-  </si>
-  <si>
-    <t>血饮自选</t>
+    <t>狂斩自选</t>
+  </si>
+  <si>
+    <t>破魂自选</t>
+  </si>
+  <si>
+    <t>血刃自选</t>
   </si>
   <si>
     <t>屠龙自选</t>
@@ -74,7 +74,7 @@
     <t>倚天自选</t>
   </si>
   <si>
-    <t>命运自选</t>
+    <t>天命自选</t>
   </si>
   <si>
     <t>升级自选</t>
@@ -1310,7 +1310,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 D4 E4 D5 E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3:E3 D4:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,D3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
